--- a/output/laminas_comunales/comunal_s_fonasa_a_2022_los_lagos.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2022_los_lagos.xlsx
@@ -375,106 +375,106 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10101</t>
+          <t>10306</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>San Juan de la Costa</t>
         </is>
       </c>
       <c r="C2">
-        <v>225012</v>
+        <v>94.8227936066713</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Osorno</t>
+          <t>Calbuco</t>
         </is>
       </c>
       <c r="C3">
-        <v>148503</v>
+        <v>94.01137942788222</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10201</t>
+          <t>10104</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Castro</t>
+          <t>Fresia</t>
         </is>
       </c>
       <c r="C4">
-        <v>44357</v>
+        <v>92.31173906508342</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10202</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ancud</t>
+          <t>Los Muermos</t>
         </is>
       </c>
       <c r="C5">
-        <v>41575</v>
+        <v>91.7566709021601</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10109</t>
+          <t>10108</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Puerto Varas</t>
+          <t>Maullín</t>
         </is>
       </c>
       <c r="C6">
-        <v>39677</v>
+        <v>91.68212739641311</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>10207</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Calbuco</t>
+          <t>Queilén</t>
         </is>
       </c>
       <c r="C7">
-        <v>35855</v>
+        <v>91.60382101558572</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10208</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Quellón</t>
+          <t>Hualaihué</t>
         </is>
       </c>
       <c r="C8">
-        <v>28224</v>
+        <v>91.03461143763411</v>
       </c>
     </row>
     <row r="9">
@@ -489,337 +489,337 @@
         </is>
       </c>
       <c r="C9">
-        <v>19638</v>
+        <v>90.93771706413521</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10105</t>
+          <t>10305</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Frutillar</t>
+          <t>Río Negro</t>
         </is>
       </c>
       <c r="C10">
-        <v>19291</v>
+        <v>90.64985925835271</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10106</t>
+          <t>10209</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Los Muermos</t>
+          <t>Quemchi</t>
         </is>
       </c>
       <c r="C11">
-        <v>17331</v>
+        <v>90.64168210044667</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10107</t>
+          <t>10302</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Llanquihue</t>
+          <t>Puerto Octay</t>
         </is>
       </c>
       <c r="C12">
-        <v>17023</v>
+        <v>90.35966670182471</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>10304</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dalcahue</t>
+          <t>Puyehue</t>
         </is>
       </c>
       <c r="C13">
-        <v>14986</v>
+        <v>90.31296572280179</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>10205</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Maullín</t>
+          <t>Dalcahue</t>
         </is>
       </c>
       <c r="C14">
-        <v>14825</v>
+        <v>89.83873868473113</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10305</t>
+          <t>10208</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Río Negro</t>
+          <t>Quellón</t>
         </is>
       </c>
       <c r="C15">
-        <v>14814</v>
+        <v>89.44099378881988</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10203</t>
+          <t>10307</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Chonchi</t>
+          <t>San Pablo</t>
         </is>
       </c>
       <c r="C16">
-        <v>14573</v>
+        <v>89.32745143564739</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>10103</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Puyehue</t>
+          <t>Cochamó</t>
         </is>
       </c>
       <c r="C17">
-        <v>12726</v>
+        <v>88.90913231610112</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10104</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fresia</t>
+          <t>Chaitén</t>
         </is>
       </c>
       <c r="C18">
-        <v>12283</v>
+        <v>88.85720105927888</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>San Pablo</t>
+          <t>Palena</t>
         </is>
       </c>
       <c r="C19">
-        <v>11542</v>
+        <v>88.6874260938116</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10402</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hualaihué</t>
+          <t>Futaleufú</t>
         </is>
       </c>
       <c r="C20">
-        <v>9758</v>
+        <v>88.58659588586596</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10302</t>
+          <t>10202</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Puerto Octay</t>
+          <t>Ancud</t>
         </is>
       </c>
       <c r="C21">
-        <v>8567</v>
+        <v>87.60931408702982</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10209</t>
+          <t>10210</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Quemchi</t>
+          <t>Quinchao</t>
         </is>
       </c>
       <c r="C22">
-        <v>8320</v>
+        <v>87.45866792631082</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10306</t>
+          <t>10206</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>San Juan de la Costa</t>
+          <t>Puqueldón</t>
         </is>
       </c>
       <c r="C23">
-        <v>8187</v>
+        <v>87.29136862184072</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10210</t>
+          <t>10203</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Quinchao</t>
+          <t>Chonchi</t>
         </is>
       </c>
       <c r="C24">
-        <v>7406</v>
+        <v>86.10848499172772</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10207</t>
+          <t>10204</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Queilén</t>
+          <t>Curaco de Vélez</t>
         </is>
       </c>
       <c r="C25">
-        <v>5466</v>
+        <v>86.00345593680572</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10401</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Chaitén</t>
+          <t>Llanquihue</t>
         </is>
       </c>
       <c r="C26">
-        <v>4362</v>
+        <v>85.81871345029239</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10103</t>
+          <t>10105</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cochamó</t>
+          <t>Frutillar</t>
         </is>
       </c>
       <c r="C27">
-        <v>3904</v>
+        <v>85.35085390673392</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10206</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Puqueldón</t>
+          <t>Osorno</t>
         </is>
       </c>
       <c r="C28">
-        <v>3661</v>
+        <v>83.82138785094206</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Curaco de Vélez</t>
+          <t>Castro</t>
         </is>
       </c>
       <c r="C29">
-        <v>3484</v>
+        <v>81.84401350628264</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Futaleufú</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="C30">
-        <v>2670</v>
+        <v>81.54440490255057</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>10109</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Palena</t>
+          <t>Puerto Varas</t>
         </is>
       </c>
       <c r="C31">
-        <v>2250</v>
+        <v>68.57532968077568</v>
       </c>
     </row>
   </sheetData>
@@ -875,7 +875,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a FONASA</t>
+          <t>Porcentaje de residentes afiliados a FONASA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
